--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2B59CBE7123C1C1B573C91B15D8B00347CADE5D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78697DC-6BE5-474A-8F48-716307C1F421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>材料名称</t>
   </si>
@@ -209,6 +209,15 @@
   </si>
   <si>
     <t>空水瓶</t>
+  </si>
+  <si>
+    <t>在晒架上由一张动物毛皮晒制而成，是游戏中必不可少的资源，无论前期还是后期，皮革都是制作装备的主要材料之一，新手可在悲伤的夜晚或者迷宫刷取</t>
+  </si>
+  <si>
+    <t>在缝纫台上由2个布料制作而成，是游戏中必不可少的资源，无论前期还是后期，厚布都是制作护甲的主要材料之一，新手可在悲伤的夜晚或者迷宫刷取</t>
+  </si>
+  <si>
+    <t>在熔炉中由一块铜锭+一块锡矿烧制而成，不过在迷宫可以无限刷取现成的青铜锭，老玩家实际上很少自己烧制青铜锭</t>
   </si>
 </sst>
 </file>
@@ -576,23 +585,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B2" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B3" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78697DC-6BE5-474A-8F48-716307C1F421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3056EFE8-AEBF-4B1D-9551-45E5A93CD8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -224,7 +224,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,13 +238,38 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -259,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -268,6 +293,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,7 +657,7 @@
       <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3"/>
@@ -688,7 +717,7 @@
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="3"/>
@@ -706,7 +735,7 @@
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="3"/>
@@ -724,19 +753,19 @@
       <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="3"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
+      <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="3"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+      <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="3"/>
@@ -766,7 +795,7 @@
       <c r="B30" s="3"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
+      <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="3"/>
@@ -796,25 +825,25 @@
       <c r="B35" s="3"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
+      <c r="A36" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B36" s="3"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
+      <c r="A37" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B37" s="3"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+      <c r="A38" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B38" s="3"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B39" s="3"/>
@@ -856,7 +885,7 @@
       <c r="B45" s="3"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
+      <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B46" s="3"/>
@@ -874,13 +903,13 @@
       <c r="B48" s="3"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
+      <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B49" s="3"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
+      <c r="A50" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B50" s="3"/>
@@ -892,37 +921,37 @@
       <c r="B51" s="3"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
+      <c r="A52" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B52" s="3"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
+      <c r="A53" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B53" s="3"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
+      <c r="A54" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="3"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
+      <c r="A55" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B55" s="3"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
+      <c r="A56" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B56" s="3"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
+      <c r="A57" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B57" s="3"/>
@@ -934,7 +963,7 @@
       <c r="B58" s="3"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
+      <c r="A59" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B59" s="3"/>

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3056EFE8-AEBF-4B1D-9551-45E5A93CD8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF92F4A9-E371-477E-B83D-6C8D2A088EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>材料名称</t>
   </si>
@@ -31,12 +31,21 @@
     <t>厚布</t>
   </si>
   <si>
+    <t>在缝纫台上由2个布料制作而成，是游戏中必不可少的资源，无论前期还是后期，厚布都是制作护甲的主要材料之一，新手可在悲伤的夜晚或者迷宫刷取</t>
+  </si>
+  <si>
     <t>皮革</t>
   </si>
   <si>
+    <t>在晒架上由一张动物毛皮晒制而成，是游戏中必不可少的资源，无论前期还是后期，皮革都是制作装备的主要材料之一，新手可在悲伤的夜晚或者迷宫刷取</t>
+  </si>
+  <si>
     <t>青铜锭</t>
   </si>
   <si>
+    <t>在熔炉中由一块铜锭+一块锡矿烧制而成，不过在迷宫可以无限刷取现成的青铜锭，老玩家实际上很少自己烧制青铜锭</t>
+  </si>
+  <si>
     <t>铁锭</t>
   </si>
   <si>
@@ -211,13 +220,46 @@
     <t>空水瓶</t>
   </si>
   <si>
-    <t>在晒架上由一张动物毛皮晒制而成，是游戏中必不可少的资源，无论前期还是后期，皮革都是制作装备的主要材料之一，新手可在悲伤的夜晚或者迷宫刷取</t>
-  </si>
-  <si>
-    <t>在缝纫台上由2个布料制作而成，是游戏中必不可少的资源，无论前期还是后期，厚布都是制作护甲的主要材料之一，新手可在悲伤的夜晚或者迷宫刷取</t>
-  </si>
-  <si>
-    <t>在熔炉中由一块铜锭+一块锡矿烧制而成，不过在迷宫可以无限刷取现成的青铜锭，老玩家实际上很少自己烧制青铜锭</t>
+    <t>U形钉</t>
+  </si>
+  <si>
+    <t>魔法木材</t>
+  </si>
+  <si>
+    <t>魔法铁锭</t>
+  </si>
+  <si>
+    <t>炉架</t>
+  </si>
+  <si>
+    <t>沙漏</t>
+  </si>
+  <si>
+    <t>镜子</t>
+  </si>
+  <si>
+    <t>蜡烛</t>
+  </si>
+  <si>
+    <t>锁头</t>
+  </si>
+  <si>
+    <t>戒指</t>
+  </si>
+  <si>
+    <t>搭扣</t>
+  </si>
+  <si>
+    <t>匙子</t>
+  </si>
+  <si>
+    <t>叉子</t>
+  </si>
+  <si>
+    <t>梳子</t>
+  </si>
+  <si>
+    <t>圣餐杯</t>
   </si>
 </sst>
 </file>
@@ -284,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -296,7 +338,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -614,377 +655,461 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B22" s="3"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B24" s="3"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B25" s="3"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B26" s="3"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B29" s="3"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B30" s="3"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B31" s="3"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B32" s="3"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B33" s="3"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B34" s="3"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B35" s="3"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B36" s="3"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B37" s="3"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B38" s="3"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B39" s="3"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B40" s="3"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B41" s="3"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B42" s="3"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B43" s="3"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B44" s="3"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B45" s="3"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B46" s="3"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B47" s="3"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B48" s="3"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B49" s="3"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B50" s="3"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B51" s="3"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B52" s="3"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B53" s="3"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54" s="7" t="s">
-        <v>54</v>
+      <c r="A54" t="s">
+        <v>57</v>
       </c>
       <c r="B54" s="3"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B55" s="3"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B56" s="3"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A57" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B57" s="3"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B58" s="3"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A59" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B59" s="3"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B60" s="3"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B61" s="3"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A63" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A64" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8946914-F4AE-484E-BCB3-98BAC1CD5C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE37976-2B24-4A61-8AAA-D72A7D283C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t>材料名称</t>
   </si>
@@ -350,13 +350,154 @@
   </si>
   <si>
     <t>魔法银锭</t>
+  </si>
+  <si>
+    <t>酸液</t>
+  </si>
+  <si>
+    <t>夹具</t>
+  </si>
+  <si>
+    <t>猫抓板</t>
+  </si>
+  <si>
+    <t>槌子</t>
+  </si>
+  <si>
+    <t>缝衣针套装</t>
+  </si>
+  <si>
+    <t>大车轴</t>
+  </si>
+  <si>
+    <t>轮子</t>
+  </si>
+  <si>
+    <t>原桦木</t>
+  </si>
+  <si>
+    <t>祷告铃</t>
+  </si>
+  <si>
+    <t>地球仪</t>
+  </si>
+  <si>
+    <t>干净的羊皮纸</t>
+  </si>
+  <si>
+    <t>锥子</t>
+  </si>
+  <si>
+    <t>凿子</t>
+  </si>
+  <si>
+    <t>轴弓</t>
+  </si>
+  <si>
+    <t>皮革软管</t>
+  </si>
+  <si>
+    <t>瓶装水</t>
+  </si>
+  <si>
+    <t>接水盘</t>
+  </si>
+  <si>
+    <t>煤炭</t>
+  </si>
+  <si>
+    <t>手锯</t>
+  </si>
+  <si>
+    <t>木工刨</t>
+  </si>
+  <si>
+    <t>楔子</t>
+  </si>
+  <si>
+    <t>剪刀</t>
+  </si>
+  <si>
+    <t>训练人偶</t>
+  </si>
+  <si>
+    <t>猫咪枕头</t>
+  </si>
+  <si>
+    <t>祭坛核心</t>
+  </si>
+  <si>
+    <t>祭坛右边板</t>
+  </si>
+  <si>
+    <t>祭坛左边板</t>
+  </si>
+  <si>
+    <t>命运之书</t>
+  </si>
+  <si>
+    <t>死者之书</t>
+  </si>
+  <si>
+    <t>叛徒之血</t>
+  </si>
+  <si>
+    <t>烈酒</t>
+  </si>
+  <si>
+    <t>望远镜</t>
+  </si>
+  <si>
+    <t>蜡线</t>
+  </si>
+  <si>
+    <t>铁匠锤</t>
+  </si>
+  <si>
+    <t>铁砧</t>
+  </si>
+  <si>
+    <t>车把</t>
+  </si>
+  <si>
+    <t>宽敞的桶</t>
+  </si>
+  <si>
+    <t>帆布</t>
+  </si>
+  <si>
+    <t>横杆</t>
+  </si>
+  <si>
+    <t>舵柄</t>
+  </si>
+  <si>
+    <t>桅杆</t>
+  </si>
+  <si>
+    <t>恐狼围栏</t>
+  </si>
+  <si>
+    <t>恐狼食盆</t>
+  </si>
+  <si>
+    <t>恐狼水盆</t>
+  </si>
+  <si>
+    <t>猫咪床</t>
+  </si>
+  <si>
+    <t>猫咪食盆</t>
+  </si>
+  <si>
+    <t>猫咪水盆</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,6 +514,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -416,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -428,6 +575,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B172"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1381,6 +1530,345 @@
       </c>
       <c r="B106" s="3"/>
     </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A107" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A108" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A109" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A110" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A111" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A112" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A113" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A114" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A115" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="3"/>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A116" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A117" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A118" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A119" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A120" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A121" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A122" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A123" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A124" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A125" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A126" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A127" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A128" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A129" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A130" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A131" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A132" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A133" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A134" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A135" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A136" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A137" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A138" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A139" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A140" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A141" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A142" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A143" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A144" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A145" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A146" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A147" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A148" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A149" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A150" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A151" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A152" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A153" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A157" s="7"/>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A158" s="7"/>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A160" s="7"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A161" s="7"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A162" s="7"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A164" s="7"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A170" s="7"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A172" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-source/材料数据.xlsx
+++ b/data-source/材料数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE37976-2B24-4A61-8AAA-D72A7D283C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FD8FF0-4D90-4551-A819-2AA7B1EA1058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1543,19 +1543,19 @@
       <c r="B108" s="3"/>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A109" s="7" t="s">
+      <c r="A109" s="4" t="s">
         <v>112</v>
       </c>
       <c r="B109" s="3"/>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A110" s="7" t="s">
+      <c r="A110" s="4" t="s">
         <v>113</v>
       </c>
       <c r="B110" s="3"/>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B111" s="3"/>
@@ -1567,7 +1567,7 @@
       <c r="B112" s="3"/>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A113" s="7" t="s">
+      <c r="A113" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B113" s="3"/>
@@ -1579,7 +1579,7 @@
       <c r="B114" s="3"/>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A115" s="7" t="s">
+      <c r="A115" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B115" s="3"/>
@@ -1591,7 +1591,7 @@
       <c r="B116" s="3"/>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A117" s="7" t="s">
+      <c r="A117" s="4" t="s">
         <v>120</v>
       </c>
       <c r="B117" s="3"/>
